--- a/Data/liver_hystology_YK.xlsx
+++ b/Data/liver_hystology_YK.xlsx
@@ -8,32 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yaroslav\OneDrive\Рабочий стол\Python_repos\Python_projects_ICG_SB_RAS\Four_host_species_OF\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F97ABD-7DAF-431E-84BB-AD6F034BE5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6FBB9C-C722-4E29-967B-1390E0FB86B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="8">
   <si>
     <t>animal_number</t>
-  </si>
-  <si>
-    <t>hyperplasia</t>
-  </si>
-  <si>
-    <t>photo_number</t>
   </si>
   <si>
     <t>group</t>
@@ -42,19 +45,28 @@
     <t>ID</t>
   </si>
   <si>
-    <t>infiltration</t>
-  </si>
-  <si>
     <t>balbc_mice</t>
   </si>
   <si>
     <t>c57bl_mice</t>
+  </si>
+  <si>
+    <t>infiltration_%</t>
+  </si>
+  <si>
+    <t>hyperplasia_%</t>
+  </si>
+  <si>
+    <t>duration_month</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="172" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -72,7 +84,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -80,12 +92,106 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -366,145 +472,455 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="25.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.21875" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" customWidth="1"/>
-    <col min="6" max="6" width="23.77734375" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" customWidth="1"/>
+    <col min="6" max="6" width="29.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="12">
+        <v>3.0864197530864197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13">
+        <v>6.7901234567901234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7">
+        <v>5.5555555555555554</v>
+      </c>
+      <c r="F4" s="13">
+        <v>8.6419753086419764</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7">
+        <v>6.1728395061728394</v>
+      </c>
+      <c r="F5" s="13">
+        <v>7.1330589849108366</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9">
+        <v>5</v>
+      </c>
+      <c r="E6" s="9">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14">
+        <v>3.8065843621399176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10">
+        <v>3.7037037037037033</v>
+      </c>
+      <c r="F7" s="12">
+        <v>1.5976761074800292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13">
+        <v>2.6748971193415638</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4</v>
+      </c>
+      <c r="E10" s="7">
+        <v>7.4074074074074066</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0.98765432098765438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9">
+        <v>5</v>
+      </c>
+      <c r="E11" s="11">
+        <v>3.7037037037037033</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0.70546737213403876</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10">
+        <v>4.9382716049382713</v>
+      </c>
+      <c r="F12" s="12">
+        <v>1.7636684303350971</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.7037037037037033</v>
+      </c>
+      <c r="F13" s="13">
+        <v>3.7808641975308639</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
+        <v>1.3521457965902408</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1.6313932980599648</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5">
+        <v>5</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.4691358024691357</v>
+      </c>
+      <c r="F16" s="13">
+        <v>12.289562289562289</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="9">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9">
         <v>6</v>
       </c>
-      <c r="C3">
+      <c r="E17" s="11">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>9.8765432098765427</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2">
+        <v>1</v>
+      </c>
+      <c r="E18" s="10">
+        <v>17.283950617283949</v>
+      </c>
+      <c r="F18" s="12">
+        <v>6.6137566137566139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="5">
+        <v>3</v>
+      </c>
+      <c r="D19" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="E19" s="7">
+        <v>12.345679012345679</v>
+      </c>
+      <c r="F19" s="13">
+        <v>24.867724867724867</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="5">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5">
+        <v>3</v>
+      </c>
+      <c r="E20" s="7">
+        <v>8.6419753086419746</v>
+      </c>
+      <c r="F20" s="13">
+        <v>2.9320987654320985</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="5">
+        <v>3</v>
+      </c>
+      <c r="D21" s="5">
+        <v>4</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.7037037037037033</v>
+      </c>
+      <c r="F21" s="13">
+        <v>2.1604938271604937</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="9">
+        <v>3</v>
+      </c>
+      <c r="D22" s="9">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11">
-        <v>5</v>
+      <c r="E22" s="11">
+        <v>2.4691358024691357</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1.7636684303350971</v>
       </c>
     </row>
   </sheetData>
